--- a/para-evaluacion-1/afn.xlsx
+++ b/para-evaluacion-1/afn.xlsx
@@ -5,12 +5,14 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="53">
   <si>
     <t xml:space="preserve">contiene la subcadena 1010</t>
   </si>
@@ -118,6 +120,69 @@
   </si>
   <si>
     <t xml:space="preserve">el ante penultimo caracter es 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">convierta los siguientes AFN a AFD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aceptacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,3,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">convertir a afn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muerto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cadenas de 0s y 1s, con una subcadena de dos 0s, separada por un numero de caracteres que es multiplo de 3 ( siendo 0 caracteres contado como multiplo de 3 )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q0,Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4,Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1,Q0</t>
   </si>
 </sst>
 </file>
@@ -127,11 +192,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -147,6 +213,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -191,8 +262,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -323,151 +402,151 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="0" t="n">
+      <c r="F8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="0" t="s">
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="0" t="s">
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E27" s="0" t="n">
+      <c r="E27" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="0" t="n">
+      <c r="F27" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="D29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30" s="0" t="s">
+      <c r="E30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E31" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="0" t="s">
+      <c r="E31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="0" t="s">
+      <c r="D32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -490,507 +569,507 @@
   <dimension ref="D7:I71"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.31"/>
   </cols>
   <sheetData>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="0" t="n">
+      <c r="E10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="0" t="n">
+      <c r="F10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="0" t="n">
+      <c r="G10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="H10" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="I38" s="0" t="s">
+      <c r="H38" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E39" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H39" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I39" s="0" t="s">
+      <c r="E39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D40" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="D40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G40" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="H40" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="I40" s="0" t="s">
+      <c r="F40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="0" t="s">
+      <c r="D41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E41" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I41" s="0" t="s">
+      <c r="E41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="E42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="G42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="H42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I42" s="0" t="s">
+      <c r="I42" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E43" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H43" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I43" s="0" t="s">
+      <c r="E43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D44" s="0" t="s">
+      <c r="D44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E44" s="0" t="s">
+      <c r="E44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="G44" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H44" s="0" t="s">
+      <c r="H44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I44" s="0" t="s">
+      <c r="I44" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D45" s="0" t="s">
+      <c r="D45" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E45" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H45" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I45" s="0" t="s">
+      <c r="E45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D46" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="G46" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="H46" s="0" t="s">
+      <c r="D46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I46" s="0" t="s">
+      <c r="I46" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D47" s="0" t="s">
+      <c r="D47" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H47" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="0" t="s">
+      <c r="E47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E62" s="0" t="n">
+      <c r="E62" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="0" t="n">
+      <c r="F62" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G62" s="0" t="n">
+      <c r="G62" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="I62" s="0" t="s">
+      <c r="H62" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D63" s="0" t="s">
+      <c r="D63" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E63" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F63" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H63" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I63" s="0" t="s">
+      <c r="E63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D64" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E64" s="0" t="s">
+      <c r="D64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F64" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G64" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="H64" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="I64" s="0" t="s">
+      <c r="F64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D65" s="0" t="s">
+      <c r="D65" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E65" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H65" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I65" s="0" t="s">
+      <c r="E65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D66" s="0" t="s">
+      <c r="D66" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E66" s="0" t="s">
+      <c r="E66" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="G66" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="0" t="s">
+      <c r="H66" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I66" s="0" t="s">
+      <c r="I66" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D67" s="0" t="s">
+      <c r="D67" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E67" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H67" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I67" s="0" t="s">
+      <c r="E67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D68" s="0" t="s">
+      <c r="D68" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E68" s="0" t="s">
+      <c r="E68" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="G68" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H68" s="0" t="s">
+      <c r="H68" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="0" t="s">
+      <c r="I68" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D69" s="0" t="s">
+      <c r="D69" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E69" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F69" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H69" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I69" s="0" t="s">
+      <c r="E69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D70" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="G70" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="H70" s="0" t="s">
+      <c r="D70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H70" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I70" s="0" t="s">
+      <c r="I70" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D71" s="0" t="s">
+      <c r="D71" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E71" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="G71" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="I71" s="0" t="s">
+      <c r="E71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1014,66 +1093,407 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="C7:F31"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>6</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E10" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D20" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E23" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D26" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F27" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D31" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="D5:G39"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D5" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>10</v>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F10" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F11" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F12" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G12" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E35" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="F35" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="0" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E36" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="G36" s="0" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E37" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="F37" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="G37" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E38" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E39" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" s="0" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
